--- a/Biblioteca de Trabajo/1. ELICITACION/1.4 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V.xlsx
+++ b/Biblioteca de Trabajo/1. ELICITACION/1.4 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ERICK\Descargas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sjean\Desktop\Universidad ESPE\Sexto Semestre Ing.Software\ADSW\P2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB0F2CD-892C-46F1-A4E6-BF78B21CC65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0649FB1E-0353-4AEC-A164-617F8FD661E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formato descripción HU" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,15 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="144">
   <si>
     <t>Matriz de Marco de Trabajo de HU</t>
   </si>
@@ -83,9 +92,6 @@
     <t>REQ001</t>
   </si>
   <si>
-    <t>Administrador</t>
-  </si>
-  <si>
     <t>Alta</t>
   </si>
   <si>
@@ -137,201 +143,337 @@
     <t>PRUEBA</t>
   </si>
   <si>
-    <t>Acceso no autorizado a la información financiera del condominio.</t>
+    <t>REQ002</t>
   </si>
   <si>
-    <t>Permitir el inicio de sesión seguro mediante credenciales web válidas y asignación de roles.</t>
+    <t>REQ003</t>
   </si>
   <si>
-    <t>Para salvaguardar los datos confidenciales de expensas y asegurar que cada usuario actúe según su perfil delimitado.</t>
+    <t>REQ004</t>
   </si>
   <si>
-    <t>Administrador, Copropietario</t>
+    <t>REQ005</t>
   </si>
   <si>
-    <t>Desarrollar el formulario de Login Web. Validar credenciales contra la base de datos de AliGest. Generar el token de sesión, evaluar el rol del usuario (Administrador o Copropietario) y redirigir al respectivo Dashboard. Registrar el acceso en la pista de auditoría.</t>
+    <t>REQ006</t>
   </si>
   <si>
-    <t>Andrés Cedeño</t>
+    <t>REQ007</t>
   </si>
   <si>
-    <t>1. Al ingresar correo y clave correctos de un Administrador activo, ingresa al panel global.
-2. Si es Copropietario, visualiza su estado de cuenta personal.
-3. Al errar credenciales, emite mensaje de error sin comprometer datos de cuentas.</t>
+    <t>REQ008</t>
   </si>
   <si>
-    <t>RF-01. Autenticación robusta y control de accesos basado en roles básicos (RBAC) para AliGest.</t>
+    <t>REQ009</t>
   </si>
   <si>
-    <t>Autenticación y Login de Usuarios</t>
+    <t>REQ010</t>
   </si>
   <si>
-    <t>Inexistencia de un padrón digitalizado y actualizado de residentes del condominio.</t>
+    <t>REQ011</t>
   </si>
   <si>
-    <t>Permitir al Administrador registrar, actualizar y dar de baja las cuentas de los Copropietarios vinculándolos a sus departamentos.</t>
+    <t>REQ012</t>
   </si>
   <si>
-    <t>Para centralizar la base de datos de copropietarios, permitiendo una correcta asignación de expensas y comunicación.</t>
+    <t>REQ013</t>
   </si>
   <si>
-    <t>Crear formulario de gestión de Copropietarios (Cédula, Nombres, Correo, Celular, ID_Departamento). Validar que la cédula y correo electrónico no estén duplicados. Implementar borrado lógico (desactivación de cuenta) si tiene saldos pendientes.</t>
+    <t>Los usuarios no tienen un mecanismo seguro para acceder al sistema.</t>
+  </si>
+  <si>
+    <t>Los usuarios pueden olvidar su contraseña y quedar bloqueados sin acceso.</t>
+  </si>
+  <si>
+    <t>No existe control claro sobre los permisos de cada usuario.</t>
+  </si>
+  <si>
+    <t>La carga manual de copropietarios desde hojas externas puede generar errores y pérdida de tiempo.</t>
+  </si>
+  <si>
+    <t>El Administrador necesita consultar información de copropietarios sin depender de archivos Excel.</t>
+  </si>
+  <si>
+    <t>La administración necesita reportes de pagos y morosidad para tomar decisiones.</t>
+  </si>
+  <si>
+    <t>Los datos de contacto o representante de una vivienda pueden cambiar.</t>
+  </si>
+  <si>
+    <t>Pueden existir registros duplicados, incorrectos o casas que deban retirarse del sistema.</t>
+  </si>
+  <si>
+    <t>Los copropietarios no tienen una forma digital de registrar pagos realizados por transferencia o depósito.</t>
+  </si>
+  <si>
+    <t>El Administrador necesita revisar si los comprobantes subidos son válidos.</t>
+  </si>
+  <si>
+    <t>La mora se calcula manualmente y puede generar errores.</t>
+  </si>
+  <si>
+    <t>El copropietario necesita respaldo formal del pago aprobado.</t>
+  </si>
+  <si>
+    <t>Los copropietarios no siempre reciben información oportuna sobre pagos, rechazos o mora.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir iniciar sesión con usuario y contraseña.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir recuperar contraseña mediante correo electrónico.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir configurar perfiles de usuario.</t>
+  </si>
+  <si>
+    <t>El sistema deberá importar datos de copropietarios desde Excel.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir leer y consultar copropietarios registrados.</t>
+  </si>
+  <si>
+    <t>El sistema deberá generar reportes personalizados.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir modificar copropietarios.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir eliminar copropietarios en casos excepcionales.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir realizar pago de expensa mediante carga de comprobante.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir validar pagos pendientes.</t>
+  </si>
+  <si>
+    <t>El sistema deberá determinar sanción por mora automáticamente.</t>
+  </si>
+  <si>
+    <t>El sistema deberá generar comprobante digital de pago.</t>
+  </si>
+  <si>
+    <t>El sistema deberá enviar notificaciones automáticas por WhatsApp.</t>
+  </si>
+  <si>
+    <t>Para proteger la información financiera y permitir acceso según el rol del usuario.</t>
+  </si>
+  <si>
+    <t>Para restablecer el acceso sin intervención manual constante del Administrador.</t>
+  </si>
+  <si>
+    <t>Para separar las funciones del Administrador y del Copropietario, evitando accesos indebidos.</t>
+  </si>
+  <si>
+    <t>Para registrar masivamente a los copropietarios del conjunto de forma ordenada y validada.</t>
+  </si>
+  <si>
+    <t>Para visualizar datos personales, estado de cuenta y filtros de búsqueda desde el sistema.</t>
+  </si>
+  <si>
+    <t>Para obtener información trazable de pagos, deudas, morosos y estados de cuenta.</t>
+  </si>
+  <si>
+    <t>Para mantener actualizada la información de los copropietarios sin eliminar registros históricos.</t>
+  </si>
+  <si>
+    <t>Para depurar registros inválidos o duplicados, manteniendo advertencias cuando exista historial financiero.</t>
+  </si>
+  <si>
+    <t>Para registrar pagos pendientes de validación y reducir la gestión manual del Administrador.</t>
+  </si>
+  <si>
+    <t>Para aprobar o rechazar pagos, actualizar estados y controlar ingresos reales del condominio.</t>
+  </si>
+  <si>
+    <t>Para aplicar correctamente el recargo del 12% a deudas vencidas según el reglamento.</t>
+  </si>
+  <si>
+    <t>Para entregar evidencia del pago, actualizar el estado de cuenta y registrar historial financiero.</t>
+  </si>
+  <si>
+    <t>Para informar al copropietario sobre aprobación, rechazo o sanción por mora sin depender de mensajes manuales.</t>
+  </si>
+  <si>
+    <t>Administrador y Copropietario</t>
+  </si>
+  <si>
+    <t>Administrador</t>
+  </si>
+  <si>
+    <t>Copropietario</t>
+  </si>
+  <si>
+    <t>Administrador / Sistema</t>
+  </si>
+  <si>
+    <t>Implementar pantalla de login, validación de campos vacíos, verificación de credenciales, creación de sesión y redirección según perfil.</t>
+  </si>
+  <si>
+    <t>Crear opción “Olvidé mi contraseña”, validar correo, generar código de 6 dígitos, enviarlo por SMTP, validar código y actualizar contraseña cifrada.</t>
+  </si>
+  <si>
+    <t>Crear interfaz para listar usuarios, cambiar rol, asignar permisos y validar que siempre exista al menos un Administrador activo.</t>
+  </si>
+  <si>
+    <t>Implementar carga de archivo Excel, validar columnas, validar cédula, correo, teléfono, número de casa, detectar duplicados y generar credenciales temporales.</t>
+  </si>
+  <si>
+    <t>Crear tabla de consulta con filtros por casa, nombre, estado de cuenta, perfil y opción de ordenar/exportar resultados.</t>
+  </si>
+  <si>
+    <t>Implementar filtros por fecha, período, estado de pago y tipo de reporte; restringir al Copropietario a sus propios datos; exportar a PDF.</t>
+  </si>
+  <si>
+    <t>Crear búsqueda por casa/nombre, formulario de edición, validaciones de cédula, correo, teléfono y generación de nueva contraseña si cambia representante.</t>
+  </si>
+  <si>
+    <t>Implementar búsqueda, confirmación de eliminación, validación de historial de pagos/deudas, invalidación de credenciales y mensaje de advertencia.</t>
+  </si>
+  <si>
+    <t>Crear formulario de pago con período, monto, fecha, método y carga de imagen JPG/PNG/JPEG con límite de 5 MB.</t>
+  </si>
+  <si>
+    <t>Crear panel de pagos pendientes, vista del comprobante, datos del pago, estado de cuenta, botones aprobar/rechazar y motivo de rechazo.</t>
+  </si>
+  <si>
+    <t>Detectar períodos vencidos, calcular 12% sobre cada deuda, actualizar estado de cuenta y mostrar desglose de mora.</t>
+  </si>
+  <si>
+    <t>Generar número único de comprobante, aplicar pago a deudas antiguas, actualizar saldo, crear PDF y guardar historial inmutable.</t>
+  </si>
+  <si>
+    <t>Integrar API de WhatsApp Business, validar teléfono, componer mensaje según evento, enviar notificación y registrar estado de envío.</t>
   </si>
   <si>
     <t>Jeancarlo Santi</t>
   </si>
   <si>
-    <t>1. El Administrador registra un nuevo copropietario y este aparece en el listado.</t>
-  </si>
-  <si>
-    <t>3. Al actualizar los datos, la persistencia se confirma inmediatamente en grilla.</t>
-  </si>
-  <si>
-    <t>RF-02. Gestión y trazabilidad completa del padrón de copropietarios del Condominio La Primavera.</t>
-  </si>
-  <si>
-    <t>Gestión de Copropietarios</t>
-  </si>
-  <si>
-    <t>Flujo lento e informal en el reporte de pagos por parte de los residentes.</t>
-  </si>
-  <si>
-    <t>Permitir que el Copropietario registre sus pagos de expensas adjuntando la captura del comprobante de transferencia/depósito bancario.</t>
-  </si>
-  <si>
-    <t>Para agilizar el proceso de recaudación y dotar al residente de un canal formal para respaldar sus transacciones puntuales.</t>
-  </si>
-  <si>
-    <t>Copropietario</t>
-  </si>
-  <si>
-    <t>Diseñar interfaz de reporte de pagos. Habilitar la selección de la expensa a pagar. Implementar el cargador de archivos para el comprobante (formatos JPG/PNG/PDF, máx. 5MB). Almacenar el registro en estado "Pendiente de Validación" y notificar internamente.</t>
-  </si>
-  <si>
     <t>Erick Tufiño</t>
   </si>
   <si>
-    <t>1. El Copropietario completa los datos del depósito, sube el comprobante y el estado se marca como 'Pendiente'.</t>
+    <t>Andres Cedeño</t>
   </si>
   <si>
-    <t>RF-03. Registro digital del pago de expensas desde la perspectiva del residente.</t>
+    <t>15/06/2026</t>
   </si>
   <si>
-    <t>Registro de Pagos de Expensas</t>
+    <t>Ingresar credenciales válidas e inválidas. Verificar acceso correcto, mensaje de error y bloqueo después de intentos fallidos.</t>
   </si>
   <si>
-    <t>Falta de control, fraude o retrasos en la confirmación de ingresos financieros.</t>
+    <t>Solicitar recuperación con correo válido, ingresar código correcto e incorrecto, validar expiración del código y cambio de contraseña.</t>
   </si>
   <si>
-    <t>Permitir al Administrador revisar, validar o rechazar los pagos reportados por los copropietarios tras contrastar la cuenta bancaria.</t>
+    <t>Cambiar un usuario de Copropietario a Administrador y viceversa. Intentar eliminar el último administrador y verificar que el sistema lo impida.</t>
   </si>
   <si>
-    <t>Para asegurar que el saldo del condominio sea real, emitiendo el comprobante oficial solo cuando el dinero esté efectivizado.</t>
+    <t>Subir archivo válido e inválido. Verificar registros guardados, errores mostrados, duplicados detectados y generación de resumen.</t>
   </si>
   <si>
-    <t>Crear bandeja de validación de pagos pendientes. Mostrar la imagen/PDF del comprobante reportado por el usuario. Agregar botones de "Aprobar" y "Rechazar". Al rechazar, exigir el ingreso de una observación obligatoria con el motivo del descarte.</t>
+    <t>Buscar copropietarios por nombre, número de casa y filtros. Validar que los resultados coincidan con la base de datos.</t>
   </si>
   <si>
-    <t>1. Al dar clic en 'Aprobar', el pago pasa a 'Validado' y el saldo de la expensa se actualiza.</t>
+    <t>Generar reporte como Administrador y como Copropietario. Verificar que el Copropietario solo vea sus propios datos.</t>
   </si>
   <si>
-    <t>RF-04. Control administrativo y conciliación visual de los abonos reportados al condominio.</t>
+    <t>Modificar correo, teléfono o cédula. Verificar actualización en base de datos y mensaje de confirmación.</t>
   </si>
   <si>
-    <t>Validación Administrativa de Pagos</t>
+    <t>Intentar eliminar copropietario sin historial y con historial. Verificar advertencia, confirmación y eliminación correcta.</t>
   </si>
   <si>
-    <t>Cálculo manual erróneo o discrecional de penalizaciones por pagos atrasados.</t>
+    <t>Subir comprobante válido e inválido. Verificar estado “Pendiente de validación”, número de solicitud y almacenamiento del archivo.</t>
   </si>
   <si>
-    <t>Calcular de forma automática la mora del 12% anual sobre las expensas vencidas al cierre de cada periodo mensual.</t>
+    <t>Aprobar pago válido y rechazar pago con motivo. Verificar cambio de estado, generación de comprobante y notificación correspondiente.</t>
   </si>
   <si>
-    <t>Para garantizar la transparencia, exactitud y estandarización matemática en el cobro de recargos por retraso bajo normativa interna.</t>
+    <t>Crear caso con deuda vencida y verificar cálculo del 12%, total por período y deuda acumulada.</t>
   </si>
   <si>
-    <t>Sistema (Proceso Interno)</t>
+    <t>Aprobar un pago y verificar PDF generado, número de comprobante, estado de cuenta actualizado e historial registrado.</t>
   </si>
   <si>
-    <t>Implementar rutina/script de fondo para el cierre de mes. Identificar expensas no pagadas tras la fecha límite. Aplicar la fórmula de interés simple proporcional (12% anual) sobre el saldo vencido. Sumar el recargo al valor de la expensa actual del copropietario.</t>
+    <t>Simular aprobación, rechazo y mora. Verificar mensaje enviado, contenido correcto y registro exitoso/fallido.</t>
   </si>
   <si>
-    <t>1. Al ejecutarse el cierre, una expensa vencida de $100 incrementa su valor con la tasa exacta del interés mensual configurado.</t>
+    <t>Inicio de sesión seguro</t>
   </si>
   <si>
-    <t>RF-05. Motor matemático automatizado para el cálculo de mora del 12% parametrizado.</t>
+    <t>Recuperación de contraseña</t>
   </si>
   <si>
-    <t>Cálculo Automático de Mora</t>
+    <t>Configuración de perfiles</t>
   </si>
   <si>
-    <t>Falta de respaldos formales de pago para uso legal o contable de las partes.</t>
+    <t>Importación de copropietarios</t>
   </si>
   <si>
-    <t>Generar y emitir automáticamente comprobantes digitales de pago en PDF una vez que la transacción es aprobada.</t>
+    <t>Consulta de copropietarios</t>
   </si>
   <si>
-    <t>Para brindar un soporte físico/digital legal e indiscutible al copropietario sobre el cumplimiento estricto de sus obligaciones financieras.</t>
+    <t>Generación de reportes</t>
   </si>
   <si>
-    <t>Diseñar plantilla de comprobante con logo de AliGest, datos del condominio, datos del copropietario, desglose de expensa, mora aplicada y total. Integrar librería de generación PDF. Habilitar la descarga directa desde el módulo histórico de pagos.</t>
+    <t>Modificación de copropietarios</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Eliminación de copropietarios</t>
   </si>
   <si>
-    <t>1. Al aprobarse un pago, el sistema habilita el botón 'Descargar Comprobante'.</t>
+    <t>Registro de pago de expensa</t>
   </si>
   <si>
-    <t>RF-06. Generación nativa de documentos legibles en formato PDF para soporte financiero.</t>
+    <t>Validación de pagos</t>
   </si>
   <si>
-    <t>Generación de Comprobantes Digitales</t>
+    <t>Cálculo de sanción por mora</t>
   </si>
   <si>
-    <t>Desconocimiento de los residentes sobre sus deudas vigentes, provocando baja recaudación.</t>
+    <t>Generación de comprobante de pago</t>
   </si>
   <si>
-    <t>Enviar notificaciones automáticas de alertas de cobro, recordatorios de vencimiento y confirmaciones de pago mediante WhatsApp.</t>
+    <t>Notificaciones automáticas de pago</t>
   </si>
   <si>
-    <t>Para optimizar los niveles de recaudación activa mediante un canal directo de comunicación de alta tasa de apertura en los teléfonos móviles.</t>
+    <t>Es requisito base para todos los demás casos de uso.</t>
   </si>
   <si>
-    <t>Sistema, Copropietario</t>
+    <t>Caso de uso administrativo de baja frecuencia, pero importante para seguridad.</t>
   </si>
   <si>
-    <t>Configurar la integración con la API/Gateway de mensajería para WhatsApp. Diseñar las plantillas de mensajes (Estructura: Saludo, Detalle de Expensa, Fecha Límite y Enlace). Programar el disparador automático al generar deudas o confirmar recaudaciones de caja.</t>
+    <t>Pertenece a Gestionar Copropietarios. Es clave para la carga inicial de los 60 copropietarios.</t>
   </si>
   <si>
-    <t>1. Al registrarse una nueva expensa o validarse un pago, el gateway procesa la plantilla.</t>
+    <t>Caso de solo lectura, no modifica información.</t>
   </si>
   <si>
-    <t>2. Se comprueba la recepción exacta del texto dinámico en el dispositivo móvil del copropietario asignado.</t>
+    <t>Se relaciona con auditoría y transparencia financiera.</t>
   </si>
   <si>
-    <t>RF-07. Sistema de alertas integrado por pasarela externa de mensajería (WhatsApp).</t>
+    <t>Extiende el caso de uso de iniciar sesión.</t>
   </si>
   <si>
-    <t>Módulo de Notificaciones por WhatsApp</t>
+    <t>Se recomienda usar este caso antes que eliminar registros.</t>
   </si>
   <si>
-    <t>REQ007</t>
+    <t>Debe usarse con cuidado porque puede afectar reportes históricos.</t>
   </si>
   <si>
-    <t>REQ006</t>
+    <t>Pertenece a Implementar Pagos. Es una funcionalidad central del negocio.</t>
   </si>
   <si>
-    <t>REQ005</t>
+    <t>Es uno de los procesos más críticos porque afecta la contabilidad.</t>
   </si>
   <si>
-    <t>REQ004</t>
+    <t>Se ejecuta desde validar pago o automáticamente cuando corresponda.</t>
   </si>
   <si>
-    <t>REQ003</t>
+    <t>Debe respetar integridad transaccional: si falla una parte, se revierte todo.</t>
   </si>
   <si>
-    <t>REQ002</t>
+    <t>Este caso es invocado por otros casos de uso, no directamente por el usuario.</t>
   </si>
 </sst>
 </file>
@@ -450,10 +592,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -836,7 +977,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1084,9 +1225,6 @@
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1424,23 +1562,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z1003"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Z1008"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.625" customWidth="1"/>
-    <col min="2" max="2" width="6.625" customWidth="1"/>
-    <col min="3" max="3" width="25.125" customWidth="1"/>
-    <col min="4" max="4" width="31.125" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
-    <col min="7" max="7" width="39.625" customWidth="1"/>
-    <col min="8" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="32.625" customWidth="1"/>
-    <col min="14" max="15" width="20.625" customWidth="1"/>
-    <col min="16" max="26" width="9.375" customWidth="1"/>
+    <col min="1" max="1" width="4.58203125" customWidth="1"/>
+    <col min="2" max="2" width="6.58203125" customWidth="1"/>
+    <col min="3" max="3" width="25.1640625" customWidth="1"/>
+    <col min="4" max="4" width="31.08203125" customWidth="1"/>
+    <col min="5" max="5" width="20.58203125" customWidth="1"/>
+    <col min="6" max="6" width="13.08203125" customWidth="1"/>
+    <col min="7" max="7" width="39.6640625" customWidth="1"/>
+    <col min="8" max="12" width="10.58203125" customWidth="1"/>
+    <col min="13" max="13" width="32.6640625" customWidth="1"/>
+    <col min="14" max="15" width="20.58203125" customWidth="1"/>
+    <col min="16" max="26" width="9.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1468,7 +1606,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="14" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1526,7 +1664,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1616,43 +1754,43 @@
         <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
-      <c r="D6" s="106" t="s">
-        <v>35</v>
+      <c r="D6" s="6" t="s">
+        <v>58</v>
       </c>
-      <c r="E6" s="106" t="s">
-        <v>36</v>
+      <c r="E6" s="6" t="s">
+        <v>71</v>
       </c>
-      <c r="F6" s="106" t="s">
-        <v>37</v>
+      <c r="F6" s="6" t="s">
+        <v>84</v>
       </c>
-      <c r="G6" s="106" t="s">
-        <v>38</v>
+      <c r="G6" s="6" t="s">
+        <v>88</v>
       </c>
-      <c r="H6" s="106" t="s">
-        <v>39</v>
+      <c r="H6" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="I6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
-      <c r="J6" s="7">
-        <v>46188</v>
+      <c r="J6" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
@@ -1668,47 +1806,47 @@
     </row>
     <row r="7" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="106" t="s">
-        <v>98</v>
+      <c r="B7" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="6">
+        <v>4</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="6">
-        <v>6</v>
-      </c>
-      <c r="J7" s="11">
-        <v>46191</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="L7" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1724,47 +1862,47 @@
     </row>
     <row r="8" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
-      <c r="B8" s="106" t="s">
-        <v>97</v>
+      <c r="B8" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="I8" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
-      <c r="J8" s="11">
-        <v>46193</v>
+      <c r="J8" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1780,47 +1918,47 @@
     </row>
     <row r="9" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="106" t="s">
-        <v>96</v>
+      <c r="B9" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>62</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="6">
+        <v>8</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="6">
-        <v>5</v>
-      </c>
-      <c r="J9" s="11">
-        <v>46195</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="L9" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1836,47 +1974,47 @@
     </row>
     <row r="10" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
-      <c r="B10" s="106" t="s">
-        <v>95</v>
+      <c r="B10" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="I10" s="6">
         <v>5</v>
       </c>
-      <c r="J10" s="11">
-        <v>46198</v>
+      <c r="J10" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1892,47 +2030,47 @@
     </row>
     <row r="11" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="106" t="s">
-        <v>94</v>
+      <c r="B11" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="F11" s="6" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="I11" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
-      <c r="J11" s="11">
-        <v>46201</v>
+      <c r="J11" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1948,47 +2086,47 @@
     </row>
     <row r="12" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="106" t="s">
-        <v>93</v>
+      <c r="B12" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="G12" s="12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="I12" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" s="11">
-        <v>46203</v>
+        <v>46060</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -2002,24 +2140,50 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="B13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="6">
+        <v>4</v>
+      </c>
+      <c r="J13" s="11">
+        <v>46061</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="M13" s="6" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="13"/>
+      <c r="N13" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>125</v>
+      </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -2032,10 +2196,49 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
-      <c r="M14" t="s">
-        <v>49</v>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="6">
+        <v>7</v>
+      </c>
+      <c r="J14" s="11">
+        <v>46062</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -2049,22 +2252,50 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="1"/>
+      <c r="B15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="6">
+        <v>8</v>
+      </c>
+      <c r="J15" s="11">
+        <v>46063</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>127</v>
+      </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -2077,22 +2308,50 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="1"/>
+      <c r="B16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="6">
+        <v>6</v>
+      </c>
+      <c r="J16" s="11">
+        <v>46064</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>128</v>
+      </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -2105,22 +2364,50 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="1"/>
+      <c r="B17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="6">
+        <v>7</v>
+      </c>
+      <c r="J17" s="11">
+        <v>46065</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>129</v>
+      </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -2133,22 +2420,50 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="18"/>
+      <c r="B18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="6">
+        <v>6</v>
+      </c>
+      <c r="J18" s="11">
+        <v>46066</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>130</v>
+      </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -2161,22 +2476,8 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="18"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -2189,22 +2490,22 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="18"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -2217,22 +2518,22 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="18"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -2247,22 +2548,20 @@
     </row>
     <row r="22" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="15"/>
-      <c r="O22" s="20"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -2275,22 +2574,22 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="1"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="18"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2303,22 +2602,22 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="1"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="18"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2331,22 +2630,22 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="1"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="18"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -2359,22 +2658,22 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="1"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="18"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
@@ -2387,22 +2686,24 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="1"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="15"/>
+      <c r="O27" s="20"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
@@ -2426,7 +2727,7 @@
       <c r="H28" s="5"/>
       <c r="I28" s="21"/>
       <c r="J28" s="21"/>
-      <c r="K28" s="23"/>
+      <c r="K28" s="22"/>
       <c r="L28" s="21"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
@@ -2479,11 +2780,11 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
+      <c r="H30" s="19"/>
       <c r="I30" s="21"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="21"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="1"/>
@@ -2509,9 +2810,9 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="21"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="21"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="1"/>
@@ -2537,13 +2838,9 @@
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="21"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L32" s="22" t="s">
-        <v>22</v>
-      </c>
+      <c r="J32" s="21"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="21"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="1"/>
@@ -2569,13 +2866,9 @@
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="21"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L33" s="22" t="s">
-        <v>19</v>
-      </c>
+      <c r="J33" s="21"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="21"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="1"/>
@@ -2601,13 +2894,9 @@
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="21"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="J34" s="21"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="21"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="1"/>
@@ -2634,10 +2923,8 @@
       <c r="H35" s="5"/>
       <c r="I35" s="21"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22" t="s">
-        <v>24</v>
-      </c>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="1"/>
@@ -2692,8 +2979,12 @@
       <c r="H37" s="5"/>
       <c r="I37" s="21"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="K37" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>21</v>
+      </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="1"/>
@@ -2709,7 +3000,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2720,8 +3011,12 @@
       <c r="H38" s="5"/>
       <c r="I38" s="21"/>
       <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
+      <c r="K38" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="22" t="s">
+        <v>18</v>
+      </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="1"/>
@@ -2737,7 +3032,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2748,8 +3043,12 @@
       <c r="H39" s="5"/>
       <c r="I39" s="21"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
+      <c r="K39" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>17</v>
+      </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="1"/>
@@ -2765,7 +3064,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2775,9 +3074,11 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
+      <c r="J40" s="5"/>
       <c r="K40" s="22"/>
-      <c r="L40" s="21"/>
+      <c r="L40" s="22" t="s">
+        <v>23</v>
+      </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="1"/>
@@ -2793,7 +3094,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2803,9 +3104,9 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="21"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="1"/>
@@ -2821,7 +3122,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2831,9 +3132,9 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="21"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="1"/>
@@ -2859,9 +3160,9 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="21"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
       <c r="O43" s="1"/>
@@ -2887,9 +3188,9 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="21"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="1"/>
@@ -29757,10 +30058,161 @@
       <c r="Y1003" s="1"/>
       <c r="Z1003" s="1"/>
     </row>
+    <row r="1004" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1004" s="5"/>
+      <c r="B1004" s="5"/>
+      <c r="C1004" s="5"/>
+      <c r="D1004" s="5"/>
+      <c r="E1004" s="5"/>
+      <c r="F1004" s="5"/>
+      <c r="G1004" s="5"/>
+      <c r="H1004" s="5"/>
+      <c r="I1004" s="21"/>
+      <c r="J1004" s="21"/>
+      <c r="K1004" s="22"/>
+      <c r="L1004" s="21"/>
+      <c r="M1004" s="5"/>
+      <c r="N1004" s="5"/>
+      <c r="O1004" s="1"/>
+      <c r="P1004" s="1"/>
+      <c r="Q1004" s="1"/>
+      <c r="R1004" s="1"/>
+      <c r="S1004" s="1"/>
+      <c r="T1004" s="1"/>
+      <c r="U1004" s="1"/>
+      <c r="V1004" s="1"/>
+      <c r="W1004" s="1"/>
+      <c r="X1004" s="1"/>
+      <c r="Y1004" s="1"/>
+      <c r="Z1004" s="1"/>
+    </row>
+    <row r="1005" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1005" s="5"/>
+      <c r="B1005" s="5"/>
+      <c r="C1005" s="5"/>
+      <c r="D1005" s="5"/>
+      <c r="E1005" s="5"/>
+      <c r="F1005" s="5"/>
+      <c r="G1005" s="5"/>
+      <c r="H1005" s="5"/>
+      <c r="I1005" s="21"/>
+      <c r="J1005" s="21"/>
+      <c r="K1005" s="22"/>
+      <c r="L1005" s="21"/>
+      <c r="M1005" s="5"/>
+      <c r="N1005" s="5"/>
+      <c r="O1005" s="1"/>
+      <c r="P1005" s="1"/>
+      <c r="Q1005" s="1"/>
+      <c r="R1005" s="1"/>
+      <c r="S1005" s="1"/>
+      <c r="T1005" s="1"/>
+      <c r="U1005" s="1"/>
+      <c r="V1005" s="1"/>
+      <c r="W1005" s="1"/>
+      <c r="X1005" s="1"/>
+      <c r="Y1005" s="1"/>
+      <c r="Z1005" s="1"/>
+    </row>
+    <row r="1006" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1006" s="5"/>
+      <c r="B1006" s="5"/>
+      <c r="C1006" s="5"/>
+      <c r="D1006" s="5"/>
+      <c r="E1006" s="5"/>
+      <c r="F1006" s="5"/>
+      <c r="G1006" s="5"/>
+      <c r="H1006" s="5"/>
+      <c r="I1006" s="21"/>
+      <c r="J1006" s="21"/>
+      <c r="K1006" s="22"/>
+      <c r="L1006" s="21"/>
+      <c r="M1006" s="5"/>
+      <c r="N1006" s="5"/>
+      <c r="O1006" s="1"/>
+      <c r="P1006" s="1"/>
+      <c r="Q1006" s="1"/>
+      <c r="R1006" s="1"/>
+      <c r="S1006" s="1"/>
+      <c r="T1006" s="1"/>
+      <c r="U1006" s="1"/>
+      <c r="V1006" s="1"/>
+      <c r="W1006" s="1"/>
+      <c r="X1006" s="1"/>
+      <c r="Y1006" s="1"/>
+      <c r="Z1006" s="1"/>
+    </row>
+    <row r="1007" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1007" s="5"/>
+      <c r="B1007" s="5"/>
+      <c r="C1007" s="5"/>
+      <c r="D1007" s="5"/>
+      <c r="E1007" s="5"/>
+      <c r="F1007" s="5"/>
+      <c r="G1007" s="5"/>
+      <c r="H1007" s="5"/>
+      <c r="I1007" s="21"/>
+      <c r="J1007" s="21"/>
+      <c r="K1007" s="22"/>
+      <c r="L1007" s="21"/>
+      <c r="M1007" s="5"/>
+      <c r="N1007" s="5"/>
+      <c r="O1007" s="1"/>
+      <c r="P1007" s="1"/>
+      <c r="Q1007" s="1"/>
+      <c r="R1007" s="1"/>
+      <c r="S1007" s="1"/>
+      <c r="T1007" s="1"/>
+      <c r="U1007" s="1"/>
+      <c r="V1007" s="1"/>
+      <c r="W1007" s="1"/>
+      <c r="X1007" s="1"/>
+      <c r="Y1007" s="1"/>
+      <c r="Z1007" s="1"/>
+    </row>
+    <row r="1008" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1008" s="5"/>
+      <c r="B1008" s="5"/>
+      <c r="C1008" s="5"/>
+      <c r="D1008" s="5"/>
+      <c r="E1008" s="5"/>
+      <c r="F1008" s="5"/>
+      <c r="G1008" s="5"/>
+      <c r="H1008" s="5"/>
+      <c r="I1008" s="21"/>
+      <c r="J1008" s="21"/>
+      <c r="K1008" s="22"/>
+      <c r="L1008" s="21"/>
+      <c r="M1008" s="5"/>
+      <c r="N1008" s="5"/>
+      <c r="O1008" s="1"/>
+      <c r="P1008" s="1"/>
+      <c r="Q1008" s="1"/>
+      <c r="R1008" s="1"/>
+      <c r="S1008" s="1"/>
+      <c r="T1008" s="1"/>
+      <c r="U1008" s="1"/>
+      <c r="V1008" s="1"/>
+      <c r="W1008" s="1"/>
+      <c r="X1008" s="1"/>
+      <c r="Y1008" s="1"/>
+      <c r="Z1008" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:O3"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="L7:L17">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF57BB8A"/>
+        <color rgb="FFFFFFFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K6">
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -29771,7 +30223,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L14">
+  <conditionalFormatting sqref="L6:L19">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -29781,27 +30233,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L12">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF57BB8A"/>
-        <color rgb="FFFFFFFF"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K15:L22" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K20:L27" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L6:L13" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$L$32:$L$35</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L6:L18" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>$L$37:$L$40</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K6:K13" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>$K$32:$K$34</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K6:K18" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>$K$37:$K$39</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="J6:J13" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="J6:J18" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(J6))), AND(ISNUMBER(J6), LEFT(CELL("format", J6))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -29817,32 +30259,32 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Z1013"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.375" customWidth="1"/>
-    <col min="2" max="2" width="2.625" customWidth="1"/>
-    <col min="3" max="15" width="10.625" customWidth="1"/>
-    <col min="16" max="16" width="2.625" customWidth="1"/>
-    <col min="17" max="26" width="9.375" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="2.58203125" customWidth="1"/>
+    <col min="3" max="15" width="10.58203125" customWidth="1"/>
+    <col min="16" max="16" width="2.58203125" customWidth="1"/>
+    <col min="17" max="26" width="9.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:26" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
       <c r="E4" s="24"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
       <c r="E5" s="24"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -29859,7 +30301,7 @@
       <c r="O6" s="58"/>
       <c r="P6" s="59"/>
     </row>
-    <row r="7" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26"/>
       <c r="B7" s="26"/>
       <c r="C7" s="27"/>
@@ -29887,7 +30329,7 @@
       <c r="Y7" s="26"/>
       <c r="Z7" s="26"/>
     </row>
-    <row r="8" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="28"/>
       <c r="C8" s="29"/>
       <c r="D8" s="29"/>
@@ -29905,14 +30347,14 @@
       <c r="P8" s="32"/>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33"/>
       <c r="C9" s="34" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="59"/>
       <c r="G9" s="35"/>
@@ -29929,21 +30371,21 @@
       <c r="P9" s="37"/>
       <c r="Q9" s="26"/>
     </row>
-    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33"/>
       <c r="C10" s="38" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="39"/>
       <c r="E10" s="77" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,5,0)</f>
-        <v>Administrador, Copropietario</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,5,0)</f>
+        <v>Administrador y Copropietario</v>
       </c>
       <c r="F10" s="59"/>
       <c r="G10" s="40"/>
       <c r="H10" s="77" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,11,0)</f>
-        <v>Terminado</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,11,0)</f>
+        <v>En proceso</v>
       </c>
       <c r="I10" s="59"/>
       <c r="J10" s="40"/>
@@ -29955,7 +30397,7 @@
       <c r="P10" s="37"/>
       <c r="Q10" s="26"/>
     </row>
-    <row r="11" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="26"/>
       <c r="B11" s="33"/>
       <c r="C11" s="41"/>
@@ -29983,11 +30425,11 @@
       <c r="Y11" s="26"/>
       <c r="Z11" s="26"/>
     </row>
-    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="26"/>
       <c r="B12" s="33"/>
       <c r="C12" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="39"/>
       <c r="E12" s="76" t="s">
@@ -29996,7 +30438,7 @@
       <c r="F12" s="59"/>
       <c r="G12" s="40"/>
       <c r="H12" s="76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="59"/>
       <c r="J12" s="40"/>
@@ -30017,23 +30459,23 @@
       <c r="Y12" s="26"/>
       <c r="Z12" s="26"/>
     </row>
-    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26"/>
       <c r="B13" s="33"/>
       <c r="C13" s="38">
-        <f>VLOOKUP('Historia de Usuario'!C10,'Formato descripción HU'!B6:O22,8,0)</f>
-        <v>4</v>
+        <f>VLOOKUP('Historia de Usuario'!C10,'Formato descripción HU'!B6:O27,8,0)</f>
+        <v>5</v>
       </c>
       <c r="D13" s="39"/>
       <c r="E13" s="77" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,10,0)</f>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,10,0)</f>
         <v>Alta</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="40"/>
       <c r="H13" s="77" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,7,0)</f>
-        <v>Andrés Cedeño</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,7,0)</f>
+        <v>Jeancarlo Santi</v>
       </c>
       <c r="I13" s="59"/>
       <c r="J13" s="40"/>
@@ -30054,7 +30496,7 @@
       <c r="Y13" s="26"/>
       <c r="Z13" s="26"/>
     </row>
-    <row r="14" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26"/>
       <c r="B14" s="33"/>
       <c r="C14" s="36"/>
@@ -30082,34 +30524,34 @@
       <c r="Y14" s="26"/>
       <c r="Z14" s="26"/>
     </row>
-    <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
       <c r="B15" s="33"/>
       <c r="C15" s="84" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="78" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,3,0)</f>
-        <v>Permitir el inicio de sesión seguro mediante credenciales web válidas y asignación de roles.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,3,0)</f>
+        <v>El sistema deberá permitir iniciar sesión con usuario y contraseña.</v>
       </c>
       <c r="E15" s="79"/>
       <c r="F15" s="43"/>
       <c r="G15" s="84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="78" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,4,0)</f>
-        <v>Para salvaguardar los datos confidenciales de expensas y asegurar que cada usuario actúe según su perfil delimitado.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,4,0)</f>
+        <v>Para proteger la información financiera y permitir acceso según el rol del usuario.</v>
       </c>
       <c r="I15" s="87"/>
       <c r="J15" s="79"/>
       <c r="K15" s="43"/>
       <c r="L15" s="84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M15" s="89" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,6,0)</f>
-        <v>Desarrollar el formulario de Login Web. Validar credenciales contra la base de datos de AliGest. Generar el token de sesión, evaluar el rol del usuario (Administrador o Copropietario) y redirigir al respectivo Dashboard. Registrar el acceso en la pista de auditoría.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,6,0)</f>
+        <v>Implementar pantalla de login, validación de campos vacíos, verificación de credenciales, creación de sesión y redirección según perfil.</v>
       </c>
       <c r="N15" s="87"/>
       <c r="O15" s="79"/>
@@ -30125,7 +30567,7 @@
       <c r="Y15" s="26"/>
       <c r="Z15" s="26"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="33"/>
       <c r="C16" s="85"/>
@@ -30153,7 +30595,7 @@
       <c r="Y16" s="26"/>
       <c r="Z16" s="26"/>
     </row>
-    <row r="17" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
       <c r="B17" s="33"/>
       <c r="C17" s="86"/>
@@ -30181,7 +30623,7 @@
       <c r="Y17" s="26"/>
       <c r="Z17" s="26"/>
     </row>
-    <row r="18" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
       <c r="B18" s="33"/>
       <c r="C18" s="36"/>
@@ -30209,15 +30651,15 @@
       <c r="Y18" s="26"/>
       <c r="Z18" s="26"/>
     </row>
-    <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33"/>
       <c r="C19" s="96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="79"/>
       <c r="E19" s="90" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,14,0)</f>
-        <v>Autenticación y Login de Usuarios</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,14,0)</f>
+        <v>Inicio de sesión seguro</v>
       </c>
       <c r="F19" s="91"/>
       <c r="G19" s="91"/>
@@ -30232,7 +30674,7 @@
       <c r="P19" s="37"/>
       <c r="Q19" s="26"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="33"/>
       <c r="C20" s="82"/>
       <c r="D20" s="83"/>
@@ -30250,7 +30692,7 @@
       <c r="P20" s="37"/>
       <c r="Q20" s="26"/>
     </row>
-    <row r="21" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="33"/>
       <c r="C21" s="36"/>
       <c r="D21" s="36"/>
@@ -30268,18 +30710,16 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="26"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="26"/>
       <c r="B22" s="33"/>
       <c r="C22" s="97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="79"/>
       <c r="E22" s="98" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,12,0)</f>
-        <v>1. Al ingresar correo y clave correctos de un Administrador activo, ingresa al panel global.
-2. Si es Copropietario, visualiza su estado de cuenta personal.
-3. Al errar credenciales, emite mensaje de error sin comprometer datos de cuentas.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,12,0)</f>
+        <v>Ingresar credenciales válidas e inválidas. Verificar acceso correcto, mensaje de error y bloqueo después de intentos fallidos.</v>
       </c>
       <c r="F22" s="87"/>
       <c r="G22" s="87"/>
@@ -30290,8 +30730,8 @@
       </c>
       <c r="K22" s="79"/>
       <c r="L22" s="78" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,13,0)</f>
-        <v>RF-01. Autenticación robusta y control de accesos basado en roles básicos (RBAC) para AliGest.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,13,0)</f>
+        <v>Es requisito base para todos los demás casos de uso.</v>
       </c>
       <c r="M22" s="87"/>
       <c r="N22" s="87"/>
@@ -30308,7 +30748,7 @@
       <c r="Y22" s="26"/>
       <c r="Z22" s="26"/>
     </row>
-    <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="26"/>
       <c r="B23" s="33"/>
       <c r="C23" s="80"/>
@@ -30336,7 +30776,7 @@
       <c r="Y23" s="26"/>
       <c r="Z23" s="26"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="26"/>
       <c r="B24" s="33"/>
       <c r="C24" s="82"/>
@@ -30364,7 +30804,7 @@
       <c r="Y24" s="26"/>
       <c r="Z24" s="26"/>
     </row>
-    <row r="25" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="26"/>
       <c r="B25" s="44"/>
       <c r="C25" s="45"/>
@@ -30392,7 +30832,7 @@
       <c r="Y25" s="26"/>
       <c r="Z25" s="26"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
@@ -30408,7 +30848,7 @@
       <c r="Y26" s="26"/>
       <c r="Z26" s="26"/>
     </row>
-    <row r="27" spans="1:26" ht="21" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="21" x14ac:dyDescent="0.3">
       <c r="A27" s="26"/>
       <c r="B27" s="99"/>
       <c r="C27" s="61"/>
@@ -30436,7 +30876,7 @@
       <c r="Y27" s="26"/>
       <c r="Z27" s="26"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="26"/>
       <c r="B28" s="26"/>
       <c r="C28" s="27"/>
@@ -30464,7 +30904,7 @@
       <c r="Y28" s="26"/>
       <c r="Z28" s="26"/>
     </row>
-    <row r="29" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="26"/>
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
@@ -30491,7 +30931,7 @@
       <c r="Y29" s="26"/>
       <c r="Z29" s="26"/>
     </row>
-    <row r="30" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="26"/>
       <c r="C30" s="47"/>
       <c r="D30" s="48"/>
@@ -30518,7 +30958,7 @@
       <c r="Y30" s="26"/>
       <c r="Z30" s="26"/>
     </row>
-    <row r="31" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="26"/>
       <c r="B31" s="26"/>
       <c r="C31" s="47"/>
@@ -30546,7 +30986,7 @@
       <c r="Y31" s="26"/>
       <c r="Z31" s="26"/>
     </row>
-    <row r="32" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="26"/>
       <c r="B32" s="26"/>
       <c r="C32" s="52"/>
@@ -30564,7 +31004,7 @@
       <c r="O32" s="51"/>
       <c r="P32" s="26"/>
     </row>
-    <row r="33" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="26"/>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
@@ -30582,7 +31022,7 @@
       <c r="O33" s="26"/>
       <c r="P33" s="26"/>
     </row>
-    <row r="34" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="26"/>
       <c r="B34" s="26"/>
       <c r="C34" s="100"/>
@@ -30600,7 +31040,7 @@
       <c r="O34" s="61"/>
       <c r="P34" s="26"/>
     </row>
-    <row r="35" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="26"/>
       <c r="B35" s="26"/>
       <c r="C35" s="61"/>
@@ -30618,7 +31058,7 @@
       <c r="O35" s="61"/>
       <c r="P35" s="26"/>
     </row>
-    <row r="36" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="26"/>
       <c r="B36" s="26"/>
       <c r="C36" s="61"/>
@@ -30636,7 +31076,7 @@
       <c r="O36" s="61"/>
       <c r="P36" s="26"/>
     </row>
-    <row r="37" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="26"/>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -30654,7 +31094,7 @@
       <c r="O37" s="26"/>
       <c r="P37" s="26"/>
     </row>
-    <row r="38" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="26"/>
       <c r="C38" s="104"/>
       <c r="D38" s="61"/>
@@ -30671,7 +31111,7 @@
       <c r="O38" s="61"/>
       <c r="P38" s="26"/>
     </row>
-    <row r="39" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="26"/>
       <c r="C39" s="61"/>
       <c r="D39" s="61"/>
@@ -30688,7 +31128,7 @@
       <c r="O39" s="61"/>
       <c r="P39" s="26"/>
     </row>
-    <row r="40" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
@@ -30705,7 +31145,7 @@
       <c r="O40" s="26"/>
       <c r="P40" s="26"/>
     </row>
-    <row r="41" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26"/>
       <c r="B41" s="26"/>
       <c r="C41" s="100"/>
@@ -30723,7 +31163,7 @@
       <c r="O41" s="61"/>
       <c r="P41" s="26"/>
     </row>
-    <row r="42" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="26"/>
       <c r="B42" s="26"/>
       <c r="C42" s="61"/>
@@ -30741,7 +31181,7 @@
       <c r="O42" s="61"/>
       <c r="P42" s="26"/>
     </row>
-    <row r="43" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26"/>
       <c r="B43" s="26"/>
       <c r="C43" s="61"/>
@@ -30759,7 +31199,7 @@
       <c r="O43" s="61"/>
       <c r="P43" s="26"/>
     </row>
-    <row r="44" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="26"/>
       <c r="B44" s="26"/>
       <c r="C44" s="26"/>
@@ -30777,7 +31217,7 @@
       <c r="O44" s="26"/>
       <c r="P44" s="26"/>
     </row>
-    <row r="45" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="26"/>
       <c r="B45" s="26"/>
       <c r="C45" s="26"/>
@@ -30795,7 +31235,7 @@
       <c r="O45" s="26"/>
       <c r="P45" s="26"/>
     </row>
-    <row r="46" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A46" s="26"/>
       <c r="B46" s="68"/>
       <c r="C46" s="61"/>
@@ -30813,7 +31253,7 @@
       <c r="O46" s="61"/>
       <c r="P46" s="61"/>
     </row>
-    <row r="47" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="26"/>
       <c r="B47" s="26"/>
       <c r="C47" s="26"/>
@@ -30831,7 +31271,7 @@
       <c r="O47" s="26"/>
       <c r="P47" s="26"/>
     </row>
-    <row r="48" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26"/>
       <c r="B48" s="26"/>
       <c r="C48" s="26"/>
@@ -30849,7 +31289,7 @@
       <c r="O48" s="26"/>
       <c r="P48" s="26"/>
     </row>
-    <row r="49" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="26"/>
       <c r="B49" s="26"/>
       <c r="C49" s="54"/>
@@ -30867,7 +31307,7 @@
       <c r="O49" s="26"/>
       <c r="P49" s="26"/>
     </row>
-    <row r="50" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="26"/>
       <c r="B50" s="26"/>
       <c r="C50" s="55"/>
@@ -30885,7 +31325,7 @@
       <c r="O50" s="26"/>
       <c r="P50" s="26"/>
     </row>
-    <row r="51" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="26"/>
       <c r="B51" s="26"/>
       <c r="C51" s="26"/>
@@ -30903,7 +31343,7 @@
       <c r="O51" s="26"/>
       <c r="P51" s="26"/>
     </row>
-    <row r="52" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="26"/>
       <c r="B52" s="26"/>
       <c r="C52" s="54"/>
@@ -30921,7 +31361,7 @@
       <c r="O52" s="26"/>
       <c r="P52" s="26"/>
     </row>
-    <row r="53" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="26"/>
       <c r="B53" s="26"/>
       <c r="C53" s="55"/>
@@ -30939,7 +31379,7 @@
       <c r="O53" s="26"/>
       <c r="P53" s="26"/>
     </row>
-    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="26"/>
       <c r="B54" s="26"/>
       <c r="C54" s="26"/>
@@ -30957,7 +31397,7 @@
       <c r="O54" s="26"/>
       <c r="P54" s="26"/>
     </row>
-    <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="26"/>
       <c r="B55" s="26"/>
       <c r="C55" s="60"/>
@@ -30975,7 +31415,7 @@
       <c r="O55" s="61"/>
       <c r="P55" s="26"/>
     </row>
-    <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="26"/>
       <c r="B56" s="26"/>
       <c r="C56" s="61"/>
@@ -30993,7 +31433,7 @@
       <c r="O56" s="61"/>
       <c r="P56" s="26"/>
     </row>
-    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="26"/>
       <c r="B57" s="26"/>
       <c r="C57" s="61"/>
@@ -31011,7 +31451,7 @@
       <c r="O57" s="61"/>
       <c r="P57" s="26"/>
     </row>
-    <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="26"/>
       <c r="B58" s="26"/>
       <c r="C58" s="26"/>
@@ -31029,7 +31469,7 @@
       <c r="O58" s="26"/>
       <c r="P58" s="26"/>
     </row>
-    <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="26"/>
       <c r="B59" s="26"/>
       <c r="C59" s="64"/>
@@ -31047,7 +31487,7 @@
       <c r="O59" s="61"/>
       <c r="P59" s="26"/>
     </row>
-    <row r="60" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="26"/>
       <c r="B60" s="26"/>
       <c r="C60" s="61"/>
@@ -31065,7 +31505,7 @@
       <c r="O60" s="61"/>
       <c r="P60" s="26"/>
     </row>
-    <row r="61" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="26"/>
       <c r="B61" s="26"/>
       <c r="C61" s="26"/>
@@ -31083,7 +31523,7 @@
       <c r="O61" s="26"/>
       <c r="P61" s="26"/>
     </row>
-    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="26"/>
       <c r="B62" s="26"/>
       <c r="C62" s="60"/>
@@ -31101,7 +31541,7 @@
       <c r="O62" s="61"/>
       <c r="P62" s="26"/>
     </row>
-    <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="26"/>
       <c r="B63" s="26"/>
       <c r="C63" s="61"/>
@@ -31119,7 +31559,7 @@
       <c r="O63" s="61"/>
       <c r="P63" s="26"/>
     </row>
-    <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="26"/>
       <c r="B64" s="26"/>
       <c r="C64" s="61"/>
@@ -31137,7 +31577,7 @@
       <c r="O64" s="61"/>
       <c r="P64" s="26"/>
     </row>
-    <row r="65" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="26"/>
       <c r="B65" s="26"/>
       <c r="C65" s="26"/>
@@ -31155,8 +31595,8 @@
       <c r="O65" s="26"/>
       <c r="P65" s="26"/>
     </row>
-    <row r="66" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="26"/>
       <c r="B67" s="68"/>
       <c r="C67" s="61"/>
@@ -31174,7 +31614,7 @@
       <c r="O67" s="61"/>
       <c r="P67" s="61"/>
     </row>
-    <row r="68" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="26"/>
       <c r="B68" s="68"/>
       <c r="C68" s="61"/>
@@ -31192,7 +31632,7 @@
       <c r="O68" s="61"/>
       <c r="P68" s="61"/>
     </row>
-    <row r="69" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="26"/>
       <c r="B69" s="26"/>
       <c r="C69" s="26"/>
@@ -31210,7 +31650,7 @@
       <c r="O69" s="26"/>
       <c r="P69" s="26"/>
     </row>
-    <row r="70" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="26"/>
       <c r="B70" s="26"/>
       <c r="C70" s="26"/>
@@ -31228,7 +31668,7 @@
       <c r="O70" s="26"/>
       <c r="P70" s="26"/>
     </row>
-    <row r="71" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="26"/>
       <c r="B71" s="26"/>
       <c r="C71" s="54"/>
@@ -31246,7 +31686,7 @@
       <c r="O71" s="26"/>
       <c r="P71" s="26"/>
     </row>
-    <row r="72" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="26"/>
       <c r="B72" s="26"/>
       <c r="C72" s="54"/>
@@ -31264,7 +31704,7 @@
       <c r="O72" s="26"/>
       <c r="P72" s="26"/>
     </row>
-    <row r="73" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="26"/>
       <c r="B73" s="26"/>
       <c r="C73" s="55"/>
@@ -31282,7 +31722,7 @@
       <c r="O73" s="26"/>
       <c r="P73" s="26"/>
     </row>
-    <row r="74" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="26"/>
       <c r="B74" s="26"/>
       <c r="C74" s="26"/>
@@ -31300,7 +31740,7 @@
       <c r="O74" s="26"/>
       <c r="P74" s="26"/>
     </row>
-    <row r="75" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="26"/>
       <c r="B75" s="26"/>
       <c r="C75" s="60"/>
@@ -31318,7 +31758,7 @@
       <c r="O75" s="61"/>
       <c r="P75" s="26"/>
     </row>
-    <row r="76" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="26"/>
       <c r="B76" s="26"/>
       <c r="C76" s="61"/>
@@ -31336,7 +31776,7 @@
       <c r="O76" s="61"/>
       <c r="P76" s="26"/>
     </row>
-    <row r="77" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="26"/>
       <c r="B77" s="26"/>
       <c r="C77" s="61"/>
@@ -31354,7 +31794,7 @@
       <c r="O77" s="61"/>
       <c r="P77" s="26"/>
     </row>
-    <row r="78" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="26"/>
       <c r="B78" s="26"/>
       <c r="C78" s="26"/>
@@ -31372,7 +31812,7 @@
       <c r="O78" s="26"/>
       <c r="P78" s="26"/>
     </row>
-    <row r="79" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="26"/>
       <c r="B79" s="26"/>
       <c r="C79" s="64"/>
@@ -31390,7 +31830,7 @@
       <c r="O79" s="61"/>
       <c r="P79" s="26"/>
     </row>
-    <row r="80" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="26"/>
       <c r="B80" s="26"/>
       <c r="C80" s="61"/>
@@ -31408,7 +31848,7 @@
       <c r="O80" s="61"/>
       <c r="P80" s="26"/>
     </row>
-    <row r="81" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="26"/>
       <c r="B81" s="26"/>
       <c r="C81" s="26"/>
@@ -31426,7 +31866,7 @@
       <c r="O81" s="26"/>
       <c r="P81" s="26"/>
     </row>
-    <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="26"/>
       <c r="B82" s="26"/>
       <c r="C82" s="60"/>
@@ -31444,7 +31884,7 @@
       <c r="O82" s="61"/>
       <c r="P82" s="26"/>
     </row>
-    <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="26"/>
       <c r="B83" s="26"/>
       <c r="C83" s="61"/>
@@ -31462,7 +31902,7 @@
       <c r="O83" s="61"/>
       <c r="P83" s="26"/>
     </row>
-    <row r="84" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26"/>
       <c r="B84" s="26"/>
       <c r="C84" s="61"/>
@@ -31480,7 +31920,7 @@
       <c r="O84" s="61"/>
       <c r="P84" s="26"/>
     </row>
-    <row r="85" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="26"/>
       <c r="C85" s="26"/>
       <c r="D85" s="26"/>
@@ -31497,10 +31937,10 @@
       <c r="O85" s="26"/>
       <c r="P85" s="26"/>
     </row>
-    <row r="86" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="26"/>
     </row>
-    <row r="87" spans="1:16" ht="21" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A87" s="26"/>
       <c r="B87" s="68"/>
       <c r="C87" s="61"/>
@@ -31518,7 +31958,7 @@
       <c r="O87" s="61"/>
       <c r="P87" s="61"/>
     </row>
-    <row r="88" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="26"/>
       <c r="B88" s="26"/>
       <c r="C88" s="26"/>
@@ -31536,7 +31976,7 @@
       <c r="O88" s="26"/>
       <c r="P88" s="26"/>
     </row>
-    <row r="89" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="26"/>
       <c r="B89" s="26"/>
       <c r="C89" s="26"/>
@@ -31554,7 +31994,7 @@
       <c r="O89" s="26"/>
       <c r="P89" s="26"/>
     </row>
-    <row r="90" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="26"/>
       <c r="B90" s="26"/>
       <c r="C90" s="54"/>
@@ -31572,7 +32012,7 @@
       <c r="O90" s="26"/>
       <c r="P90" s="26"/>
     </row>
-    <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="26"/>
       <c r="B91" s="26"/>
       <c r="C91" s="55"/>
@@ -31590,7 +32030,7 @@
       <c r="O91" s="26"/>
       <c r="P91" s="26"/>
     </row>
-    <row r="92" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="26"/>
       <c r="B92" s="26"/>
       <c r="C92" s="26"/>
@@ -31608,7 +32048,7 @@
       <c r="O92" s="26"/>
       <c r="P92" s="26"/>
     </row>
-    <row r="93" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="26"/>
       <c r="B93" s="26"/>
       <c r="C93" s="60"/>
@@ -31626,7 +32066,7 @@
       <c r="O93" s="61"/>
       <c r="P93" s="26"/>
     </row>
-    <row r="94" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="26"/>
       <c r="B94" s="26"/>
       <c r="C94" s="61"/>
@@ -31644,7 +32084,7 @@
       <c r="O94" s="61"/>
       <c r="P94" s="26"/>
     </row>
-    <row r="95" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="26"/>
       <c r="B95" s="26"/>
       <c r="C95" s="61"/>
@@ -31662,7 +32102,7 @@
       <c r="O95" s="61"/>
       <c r="P95" s="26"/>
     </row>
-    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="26"/>
       <c r="B96" s="26"/>
       <c r="C96" s="26"/>
@@ -31680,7 +32120,7 @@
       <c r="O96" s="26"/>
       <c r="P96" s="26"/>
     </row>
-    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="26"/>
       <c r="B97" s="26"/>
       <c r="C97" s="64"/>
@@ -31698,7 +32138,7 @@
       <c r="O97" s="61"/>
       <c r="P97" s="26"/>
     </row>
-    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="26"/>
       <c r="B98" s="26"/>
       <c r="C98" s="61"/>
@@ -31716,7 +32156,7 @@
       <c r="O98" s="61"/>
       <c r="P98" s="26"/>
     </row>
-    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="26"/>
       <c r="B99" s="26"/>
       <c r="C99" s="26"/>
@@ -31734,7 +32174,7 @@
       <c r="O99" s="26"/>
       <c r="P99" s="26"/>
     </row>
-    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="26"/>
       <c r="B100" s="26"/>
       <c r="C100" s="60"/>
@@ -31752,7 +32192,7 @@
       <c r="O100" s="61"/>
       <c r="P100" s="26"/>
     </row>
-    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="26"/>
       <c r="B101" s="26"/>
       <c r="C101" s="61"/>
@@ -31770,7 +32210,7 @@
       <c r="O101" s="61"/>
       <c r="P101" s="26"/>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="26"/>
       <c r="B102" s="26"/>
       <c r="C102" s="61"/>
@@ -31788,7 +32228,7 @@
       <c r="O102" s="61"/>
       <c r="P102" s="26"/>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="26"/>
       <c r="C103" s="26"/>
       <c r="D103" s="26"/>
@@ -31805,7 +32245,7 @@
       <c r="O103" s="26"/>
       <c r="P103" s="26"/>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="26"/>
       <c r="C104" s="26"/>
       <c r="D104" s="26"/>
@@ -31822,7 +32262,7 @@
       <c r="O104" s="26"/>
       <c r="P104" s="26"/>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B105" s="68"/>
       <c r="C105" s="61"/>
       <c r="D105" s="61"/>
@@ -31839,914 +32279,914 @@
       <c r="O105" s="61"/>
       <c r="P105" s="61"/>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="99">
     <mergeCell ref="E50:F50"/>
@@ -32872,7 +33312,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>'Formato descripción HU'!$B$6:$B$22</xm:f>
+            <xm:f>'Formato descripción HU'!$B$6:$B$27</xm:f>
           </x14:formula1>
           <xm:sqref>C10:C11 C50:C51</xm:sqref>
         </x14:dataValidation>

--- a/Biblioteca de Trabajo/1. ELICITACION/1.4 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V.xlsx
+++ b/Biblioteca de Trabajo/1. ELICITACION/1.4 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sjean\Desktop\Universidad ESPE\Sexto Semestre Ing.Software\ADSW\P2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ERICK\Descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0649FB1E-0353-4AEC-A164-617F8FD661E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57288DD6-B5BB-4749-B1B4-D55B94AD22C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formato descripción HU" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -179,9 +170,6 @@
     <t>REQ013</t>
   </si>
   <si>
-    <t>Los usuarios no tienen un mecanismo seguro para acceder al sistema.</t>
-  </si>
-  <si>
     <t>Los usuarios pueden olvidar su contraseña y quedar bloqueados sin acceso.</t>
   </si>
   <si>
@@ -218,9 +206,6 @@
     <t>Los copropietarios no siempre reciben información oportuna sobre pagos, rechazos o mora.</t>
   </si>
   <si>
-    <t>El sistema deberá permitir iniciar sesión con usuario y contraseña.</t>
-  </si>
-  <si>
     <t>El sistema deberá permitir recuperar contraseña mediante correo electrónico.</t>
   </si>
   <si>
@@ -255,9 +240,6 @@
   </si>
   <si>
     <t>El sistema deberá enviar notificaciones automáticas por WhatsApp.</t>
-  </si>
-  <si>
-    <t>Para proteger la información financiera y permitir acceso según el rol del usuario.</t>
   </si>
   <si>
     <t>Para restablecer el acceso sin intervención manual constante del Administrador.</t>
@@ -308,9 +290,6 @@
     <t>Administrador / Sistema</t>
   </si>
   <si>
-    <t>Implementar pantalla de login, validación de campos vacíos, verificación de credenciales, creación de sesión y redirección según perfil.</t>
-  </si>
-  <si>
     <t>Crear opción “Olvidé mi contraseña”, validar correo, generar código de 6 dígitos, enviarlo por SMTP, validar código y actualizar contraseña cifrada.</t>
   </si>
   <si>
@@ -359,9 +338,6 @@
     <t>15/06/2026</t>
   </si>
   <si>
-    <t>Ingresar credenciales válidas e inválidas. Verificar acceso correcto, mensaje de error y bloqueo después de intentos fallidos.</t>
-  </si>
-  <si>
     <t>Solicitar recuperación con correo válido, ingresar código correcto e incorrecto, validar expiración del código y cambio de contraseña.</t>
   </si>
   <si>
@@ -396,9 +372,6 @@
   </si>
   <si>
     <t>Simular aprobación, rechazo y mora. Verificar mensaje enviado, contenido correcto y registro exitoso/fallido.</t>
-  </si>
-  <si>
-    <t>Inicio de sesión seguro</t>
   </si>
   <si>
     <t>Recuperación de contraseña</t>
@@ -474,6 +447,25 @@
   </si>
   <si>
     <t>Este caso es invocado por otros casos de uso, no directamente por el usuario.</t>
+  </si>
+  <si>
+    <t>Los usuarios no tienen un mecanismo seguro para acceder al sistema ni para crear cuentas nuevas.</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir iniciar sesión con usuario/contraseña y registrar nuevos usuarios.</t>
+  </si>
+  <si>
+    <t>Para proteger la información financiera, permitir acceso según el rol del usuario y gestionar nuevos accesos.</t>
+  </si>
+  <si>
+    <t>Implementar pantalla de login, validación de campos, verificación de credenciales, redirección según perfil, maquetación de formulario de registro y persistencia de nuevos usuarios.</t>
+  </si>
+  <si>
+    <t>Ingresar credenciales válidas e inválidas en login; verificar acceso, error y bloqueo.
+Llenar el registro con datos válidos; verificar guardado en BD y clave cifrada.</t>
+  </si>
+  <si>
+    <t>Gestión de Acceso y Registro de Usuarios</t>
   </si>
 </sst>
 </file>
@@ -1563,22 +1555,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z1008"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.58203125" customWidth="1"/>
-    <col min="2" max="2" width="6.58203125" customWidth="1"/>
-    <col min="3" max="3" width="25.1640625" customWidth="1"/>
-    <col min="4" max="4" width="31.08203125" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" customWidth="1"/>
-    <col min="6" max="6" width="13.08203125" customWidth="1"/>
-    <col min="7" max="7" width="39.6640625" customWidth="1"/>
-    <col min="8" max="12" width="10.58203125" customWidth="1"/>
-    <col min="13" max="13" width="32.6640625" customWidth="1"/>
-    <col min="14" max="15" width="20.58203125" customWidth="1"/>
-    <col min="16" max="26" width="9.4140625" customWidth="1"/>
+    <col min="1" max="1" width="4.625" customWidth="1"/>
+    <col min="2" max="2" width="6.625" customWidth="1"/>
+    <col min="3" max="3" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="31.125" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="13.125" customWidth="1"/>
+    <col min="7" max="7" width="39.625" customWidth="1"/>
+    <col min="8" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="32.625" customWidth="1"/>
+    <col min="14" max="15" width="20.625" customWidth="1"/>
+    <col min="16" max="26" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1606,7 +1598,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1664,7 +1656,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1754,28 +1746,28 @@
         <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I6" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>16</v>
@@ -1784,13 +1776,13 @@
         <v>18</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
@@ -1810,28 +1802,28 @@
         <v>33</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I7" s="6">
         <v>4</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>16</v>
@@ -1840,13 +1832,13 @@
         <v>18</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1866,28 +1858,28 @@
         <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I8" s="6">
         <v>5</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>19</v>
@@ -1896,13 +1888,13 @@
         <v>18</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1922,28 +1914,28 @@
         <v>35</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I9" s="6">
         <v>8</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>16</v>
@@ -1952,13 +1944,13 @@
         <v>18</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1978,28 +1970,28 @@
         <v>36</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I10" s="6">
         <v>5</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>19</v>
@@ -2008,13 +2000,13 @@
         <v>18</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -2034,28 +2026,28 @@
         <v>37</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I11" s="6">
         <v>6</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>19</v>
@@ -2064,13 +2056,13 @@
         <v>18</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -2090,22 +2082,22 @@
         <v>38</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I12" s="6">
         <v>5</v>
@@ -2120,13 +2112,13 @@
         <v>18</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -2146,22 +2138,22 @@
         <v>39</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I13" s="6">
         <v>4</v>
@@ -2176,13 +2168,13 @@
         <v>18</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
@@ -2202,22 +2194,22 @@
         <v>40</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I14" s="6">
         <v>7</v>
@@ -2232,13 +2224,13 @@
         <v>18</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -2258,22 +2250,22 @@
         <v>41</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I15" s="6">
         <v>8</v>
@@ -2288,13 +2280,13 @@
         <v>18</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -2314,22 +2306,22 @@
         <v>42</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I16" s="6">
         <v>6</v>
@@ -2344,13 +2336,13 @@
         <v>18</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
@@ -2370,22 +2362,22 @@
         <v>43</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I17" s="6">
         <v>7</v>
@@ -2400,13 +2392,13 @@
         <v>18</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -2426,22 +2418,22 @@
         <v>44</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="G18" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I18" s="6">
         <v>6</v>
@@ -2456,13 +2448,13 @@
         <v>18</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -30203,16 +30195,6 @@
     <mergeCell ref="B3:O3"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="L7:L17">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF57BB8A"/>
-        <color rgb="FFFFFFFF"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K6">
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -30225,6 +30207,16 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L19">
     <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF57BB8A"/>
+        <color rgb="FFFFFFFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L17">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -30259,30 +30251,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Z1013"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" customWidth="1"/>
-    <col min="2" max="2" width="2.58203125" customWidth="1"/>
-    <col min="3" max="15" width="10.58203125" customWidth="1"/>
-    <col min="16" max="16" width="2.58203125" customWidth="1"/>
-    <col min="17" max="26" width="9.4140625" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="2" width="2.625" customWidth="1"/>
+    <col min="3" max="15" width="10.625" customWidth="1"/>
+    <col min="16" max="16" width="2.625" customWidth="1"/>
+    <col min="17" max="26" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:26" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
       <c r="E4" s="24"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="1:26" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
       <c r="E5" s="24"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="75" t="s">
         <v>24</v>
       </c>
@@ -30301,7 +30293,7 @@
       <c r="O6" s="58"/>
       <c r="P6" s="59"/>
     </row>
-    <row r="7" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="26"/>
       <c r="B7" s="26"/>
       <c r="C7" s="27"/>
@@ -30329,7 +30321,7 @@
       <c r="Y7" s="26"/>
       <c r="Z7" s="26"/>
     </row>
-    <row r="8" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="28"/>
       <c r="C8" s="29"/>
       <c r="D8" s="29"/>
@@ -30347,7 +30339,7 @@
       <c r="P8" s="32"/>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="33"/>
       <c r="C9" s="34" t="s">
         <v>1</v>
@@ -30371,7 +30363,7 @@
       <c r="P9" s="37"/>
       <c r="Q9" s="26"/>
     </row>
-    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="33"/>
       <c r="C10" s="38" t="s">
         <v>15</v>
@@ -30397,7 +30389,7 @@
       <c r="P10" s="37"/>
       <c r="Q10" s="26"/>
     </row>
-    <row r="11" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="26"/>
       <c r="B11" s="33"/>
       <c r="C11" s="41"/>
@@ -30425,7 +30417,7 @@
       <c r="Y11" s="26"/>
       <c r="Z11" s="26"/>
     </row>
-    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="26"/>
       <c r="B12" s="33"/>
       <c r="C12" s="34" t="s">
@@ -30459,12 +30451,12 @@
       <c r="Y12" s="26"/>
       <c r="Z12" s="26"/>
     </row>
-    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="26"/>
       <c r="B13" s="33"/>
       <c r="C13" s="38">
         <f>VLOOKUP('Historia de Usuario'!C10,'Formato descripción HU'!B6:O27,8,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" s="39"/>
       <c r="E13" s="77" t="str">
@@ -30496,7 +30488,7 @@
       <c r="Y13" s="26"/>
       <c r="Z13" s="26"/>
     </row>
-    <row r="14" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="26"/>
       <c r="B14" s="33"/>
       <c r="C14" s="36"/>
@@ -30524,7 +30516,7 @@
       <c r="Y14" s="26"/>
       <c r="Z14" s="26"/>
     </row>
-    <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="26"/>
       <c r="B15" s="33"/>
       <c r="C15" s="84" t="s">
@@ -30532,7 +30524,7 @@
       </c>
       <c r="D15" s="78" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,3,0)</f>
-        <v>El sistema deberá permitir iniciar sesión con usuario y contraseña.</v>
+        <v>El sistema deberá permitir iniciar sesión con usuario/contraseña y registrar nuevos usuarios.</v>
       </c>
       <c r="E15" s="79"/>
       <c r="F15" s="43"/>
@@ -30541,7 +30533,7 @@
       </c>
       <c r="H15" s="78" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,4,0)</f>
-        <v>Para proteger la información financiera y permitir acceso según el rol del usuario.</v>
+        <v>Para proteger la información financiera, permitir acceso según el rol del usuario y gestionar nuevos accesos.</v>
       </c>
       <c r="I15" s="87"/>
       <c r="J15" s="79"/>
@@ -30551,7 +30543,7 @@
       </c>
       <c r="M15" s="89" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,6,0)</f>
-        <v>Implementar pantalla de login, validación de campos vacíos, verificación de credenciales, creación de sesión y redirección según perfil.</v>
+        <v>Implementar pantalla de login, validación de campos, verificación de credenciales, redirección según perfil, maquetación de formulario de registro y persistencia de nuevos usuarios.</v>
       </c>
       <c r="N15" s="87"/>
       <c r="O15" s="79"/>
@@ -30567,7 +30559,7 @@
       <c r="Y15" s="26"/>
       <c r="Z15" s="26"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="26"/>
       <c r="B16" s="33"/>
       <c r="C16" s="85"/>
@@ -30595,7 +30587,7 @@
       <c r="Y16" s="26"/>
       <c r="Z16" s="26"/>
     </row>
-    <row r="17" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="26"/>
       <c r="B17" s="33"/>
       <c r="C17" s="86"/>
@@ -30623,7 +30615,7 @@
       <c r="Y17" s="26"/>
       <c r="Z17" s="26"/>
     </row>
-    <row r="18" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="26"/>
       <c r="B18" s="33"/>
       <c r="C18" s="36"/>
@@ -30651,7 +30643,7 @@
       <c r="Y18" s="26"/>
       <c r="Z18" s="26"/>
     </row>
-    <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="33"/>
       <c r="C19" s="96" t="s">
         <v>31</v>
@@ -30659,7 +30651,7 @@
       <c r="D19" s="79"/>
       <c r="E19" s="90" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,14,0)</f>
-        <v>Inicio de sesión seguro</v>
+        <v>Gestión de Acceso y Registro de Usuarios</v>
       </c>
       <c r="F19" s="91"/>
       <c r="G19" s="91"/>
@@ -30674,7 +30666,7 @@
       <c r="P19" s="37"/>
       <c r="Q19" s="26"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="33"/>
       <c r="C20" s="82"/>
       <c r="D20" s="83"/>
@@ -30692,7 +30684,7 @@
       <c r="P20" s="37"/>
       <c r="Q20" s="26"/>
     </row>
-    <row r="21" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="33"/>
       <c r="C21" s="36"/>
       <c r="D21" s="36"/>
@@ -30710,7 +30702,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="26"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="26"/>
       <c r="B22" s="33"/>
       <c r="C22" s="97" t="s">
@@ -30719,7 +30711,8 @@
       <c r="D22" s="79"/>
       <c r="E22" s="98" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O27,12,0)</f>
-        <v>Ingresar credenciales válidas e inválidas. Verificar acceso correcto, mensaje de error y bloqueo después de intentos fallidos.</v>
+        <v>Ingresar credenciales válidas e inválidas en login; verificar acceso, error y bloqueo.
+Llenar el registro con datos válidos; verificar guardado en BD y clave cifrada.</v>
       </c>
       <c r="F22" s="87"/>
       <c r="G22" s="87"/>
@@ -30748,7 +30741,7 @@
       <c r="Y22" s="26"/>
       <c r="Z22" s="26"/>
     </row>
-    <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="26"/>
       <c r="B23" s="33"/>
       <c r="C23" s="80"/>
@@ -30776,7 +30769,7 @@
       <c r="Y23" s="26"/>
       <c r="Z23" s="26"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="26"/>
       <c r="B24" s="33"/>
       <c r="C24" s="82"/>
@@ -30804,7 +30797,7 @@
       <c r="Y24" s="26"/>
       <c r="Z24" s="26"/>
     </row>
-    <row r="25" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="26"/>
       <c r="B25" s="44"/>
       <c r="C25" s="45"/>
@@ -30832,7 +30825,7 @@
       <c r="Y25" s="26"/>
       <c r="Z25" s="26"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
@@ -30848,7 +30841,7 @@
       <c r="Y26" s="26"/>
       <c r="Z26" s="26"/>
     </row>
-    <row r="27" spans="1:26" ht="21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="21" x14ac:dyDescent="0.2">
       <c r="A27" s="26"/>
       <c r="B27" s="99"/>
       <c r="C27" s="61"/>
@@ -30876,7 +30869,7 @@
       <c r="Y27" s="26"/>
       <c r="Z27" s="26"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
       <c r="B28" s="26"/>
       <c r="C28" s="27"/>
@@ -30904,7 +30897,7 @@
       <c r="Y28" s="26"/>
       <c r="Z28" s="26"/>
     </row>
-    <row r="29" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="26"/>
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
@@ -30931,7 +30924,7 @@
       <c r="Y29" s="26"/>
       <c r="Z29" s="26"/>
     </row>
-    <row r="30" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="26"/>
       <c r="C30" s="47"/>
       <c r="D30" s="48"/>
@@ -30958,7 +30951,7 @@
       <c r="Y30" s="26"/>
       <c r="Z30" s="26"/>
     </row>
-    <row r="31" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="26"/>
       <c r="B31" s="26"/>
       <c r="C31" s="47"/>
@@ -30986,7 +30979,7 @@
       <c r="Y31" s="26"/>
       <c r="Z31" s="26"/>
     </row>
-    <row r="32" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="26"/>
       <c r="B32" s="26"/>
       <c r="C32" s="52"/>
@@ -31004,7 +30997,7 @@
       <c r="O32" s="51"/>
       <c r="P32" s="26"/>
     </row>
-    <row r="33" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="26"/>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
@@ -31022,7 +31015,7 @@
       <c r="O33" s="26"/>
       <c r="P33" s="26"/>
     </row>
-    <row r="34" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="26"/>
       <c r="B34" s="26"/>
       <c r="C34" s="100"/>
@@ -31040,7 +31033,7 @@
       <c r="O34" s="61"/>
       <c r="P34" s="26"/>
     </row>
-    <row r="35" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="26"/>
       <c r="B35" s="26"/>
       <c r="C35" s="61"/>
@@ -31058,7 +31051,7 @@
       <c r="O35" s="61"/>
       <c r="P35" s="26"/>
     </row>
-    <row r="36" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="26"/>
       <c r="B36" s="26"/>
       <c r="C36" s="61"/>
@@ -31076,7 +31069,7 @@
       <c r="O36" s="61"/>
       <c r="P36" s="26"/>
     </row>
-    <row r="37" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="26"/>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -31094,7 +31087,7 @@
       <c r="O37" s="26"/>
       <c r="P37" s="26"/>
     </row>
-    <row r="38" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="26"/>
       <c r="C38" s="104"/>
       <c r="D38" s="61"/>
@@ -31111,7 +31104,7 @@
       <c r="O38" s="61"/>
       <c r="P38" s="26"/>
     </row>
-    <row r="39" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="26"/>
       <c r="C39" s="61"/>
       <c r="D39" s="61"/>
@@ -31128,7 +31121,7 @@
       <c r="O39" s="61"/>
       <c r="P39" s="26"/>
     </row>
-    <row r="40" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
@@ -31145,7 +31138,7 @@
       <c r="O40" s="26"/>
       <c r="P40" s="26"/>
     </row>
-    <row r="41" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="26"/>
       <c r="B41" s="26"/>
       <c r="C41" s="100"/>
@@ -31163,7 +31156,7 @@
       <c r="O41" s="61"/>
       <c r="P41" s="26"/>
     </row>
-    <row r="42" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="26"/>
       <c r="B42" s="26"/>
       <c r="C42" s="61"/>
@@ -31181,7 +31174,7 @@
       <c r="O42" s="61"/>
       <c r="P42" s="26"/>
     </row>
-    <row r="43" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="26"/>
       <c r="B43" s="26"/>
       <c r="C43" s="61"/>
@@ -31199,7 +31192,7 @@
       <c r="O43" s="61"/>
       <c r="P43" s="26"/>
     </row>
-    <row r="44" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="26"/>
       <c r="B44" s="26"/>
       <c r="C44" s="26"/>
@@ -31217,7 +31210,7 @@
       <c r="O44" s="26"/>
       <c r="P44" s="26"/>
     </row>
-    <row r="45" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="26"/>
       <c r="B45" s="26"/>
       <c r="C45" s="26"/>
@@ -31235,7 +31228,7 @@
       <c r="O45" s="26"/>
       <c r="P45" s="26"/>
     </row>
-    <row r="46" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="26"/>
       <c r="B46" s="68"/>
       <c r="C46" s="61"/>
@@ -31253,7 +31246,7 @@
       <c r="O46" s="61"/>
       <c r="P46" s="61"/>
     </row>
-    <row r="47" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="26"/>
       <c r="B47" s="26"/>
       <c r="C47" s="26"/>
@@ -31271,7 +31264,7 @@
       <c r="O47" s="26"/>
       <c r="P47" s="26"/>
     </row>
-    <row r="48" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="26"/>
       <c r="B48" s="26"/>
       <c r="C48" s="26"/>
@@ -31289,7 +31282,7 @@
       <c r="O48" s="26"/>
       <c r="P48" s="26"/>
     </row>
-    <row r="49" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="26"/>
       <c r="B49" s="26"/>
       <c r="C49" s="54"/>
@@ -31307,7 +31300,7 @@
       <c r="O49" s="26"/>
       <c r="P49" s="26"/>
     </row>
-    <row r="50" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26"/>
       <c r="B50" s="26"/>
       <c r="C50" s="55"/>
@@ -31325,7 +31318,7 @@
       <c r="O50" s="26"/>
       <c r="P50" s="26"/>
     </row>
-    <row r="51" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="26"/>
       <c r="B51" s="26"/>
       <c r="C51" s="26"/>
@@ -31343,7 +31336,7 @@
       <c r="O51" s="26"/>
       <c r="P51" s="26"/>
     </row>
-    <row r="52" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="26"/>
       <c r="B52" s="26"/>
       <c r="C52" s="54"/>
@@ -31361,7 +31354,7 @@
       <c r="O52" s="26"/>
       <c r="P52" s="26"/>
     </row>
-    <row r="53" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
       <c r="B53" s="26"/>
       <c r="C53" s="55"/>
@@ -31379,7 +31372,7 @@
       <c r="O53" s="26"/>
       <c r="P53" s="26"/>
     </row>
-    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="26"/>
       <c r="B54" s="26"/>
       <c r="C54" s="26"/>
@@ -31397,7 +31390,7 @@
       <c r="O54" s="26"/>
       <c r="P54" s="26"/>
     </row>
-    <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="26"/>
       <c r="B55" s="26"/>
       <c r="C55" s="60"/>
@@ -31415,7 +31408,7 @@
       <c r="O55" s="61"/>
       <c r="P55" s="26"/>
     </row>
-    <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="26"/>
       <c r="B56" s="26"/>
       <c r="C56" s="61"/>
@@ -31433,7 +31426,7 @@
       <c r="O56" s="61"/>
       <c r="P56" s="26"/>
     </row>
-    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="26"/>
       <c r="B57" s="26"/>
       <c r="C57" s="61"/>
@@ -31451,7 +31444,7 @@
       <c r="O57" s="61"/>
       <c r="P57" s="26"/>
     </row>
-    <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="26"/>
       <c r="B58" s="26"/>
       <c r="C58" s="26"/>
@@ -31469,7 +31462,7 @@
       <c r="O58" s="26"/>
       <c r="P58" s="26"/>
     </row>
-    <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="26"/>
       <c r="B59" s="26"/>
       <c r="C59" s="64"/>
@@ -31487,7 +31480,7 @@
       <c r="O59" s="61"/>
       <c r="P59" s="26"/>
     </row>
-    <row r="60" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="26"/>
       <c r="B60" s="26"/>
       <c r="C60" s="61"/>
@@ -31505,7 +31498,7 @@
       <c r="O60" s="61"/>
       <c r="P60" s="26"/>
     </row>
-    <row r="61" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="26"/>
       <c r="B61" s="26"/>
       <c r="C61" s="26"/>
@@ -31523,7 +31516,7 @@
       <c r="O61" s="26"/>
       <c r="P61" s="26"/>
     </row>
-    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="26"/>
       <c r="B62" s="26"/>
       <c r="C62" s="60"/>
@@ -31541,7 +31534,7 @@
       <c r="O62" s="61"/>
       <c r="P62" s="26"/>
     </row>
-    <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="26"/>
       <c r="B63" s="26"/>
       <c r="C63" s="61"/>
@@ -31559,7 +31552,7 @@
       <c r="O63" s="61"/>
       <c r="P63" s="26"/>
     </row>
-    <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="26"/>
       <c r="B64" s="26"/>
       <c r="C64" s="61"/>
@@ -31577,7 +31570,7 @@
       <c r="O64" s="61"/>
       <c r="P64" s="26"/>
     </row>
-    <row r="65" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="26"/>
       <c r="B65" s="26"/>
       <c r="C65" s="26"/>
@@ -31595,8 +31588,8 @@
       <c r="O65" s="26"/>
       <c r="P65" s="26"/>
     </row>
-    <row r="66" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="26"/>
       <c r="B67" s="68"/>
       <c r="C67" s="61"/>
@@ -31614,7 +31607,7 @@
       <c r="O67" s="61"/>
       <c r="P67" s="61"/>
     </row>
-    <row r="68" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="26"/>
       <c r="B68" s="68"/>
       <c r="C68" s="61"/>
@@ -31632,7 +31625,7 @@
       <c r="O68" s="61"/>
       <c r="P68" s="61"/>
     </row>
-    <row r="69" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="26"/>
       <c r="B69" s="26"/>
       <c r="C69" s="26"/>
@@ -31650,7 +31643,7 @@
       <c r="O69" s="26"/>
       <c r="P69" s="26"/>
     </row>
-    <row r="70" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="26"/>
       <c r="B70" s="26"/>
       <c r="C70" s="26"/>
@@ -31668,7 +31661,7 @@
       <c r="O70" s="26"/>
       <c r="P70" s="26"/>
     </row>
-    <row r="71" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="26"/>
       <c r="B71" s="26"/>
       <c r="C71" s="54"/>
@@ -31686,7 +31679,7 @@
       <c r="O71" s="26"/>
       <c r="P71" s="26"/>
     </row>
-    <row r="72" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="26"/>
       <c r="B72" s="26"/>
       <c r="C72" s="54"/>
@@ -31704,7 +31697,7 @@
       <c r="O72" s="26"/>
       <c r="P72" s="26"/>
     </row>
-    <row r="73" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="26"/>
       <c r="B73" s="26"/>
       <c r="C73" s="55"/>
@@ -31722,7 +31715,7 @@
       <c r="O73" s="26"/>
       <c r="P73" s="26"/>
     </row>
-    <row r="74" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="26"/>
       <c r="B74" s="26"/>
       <c r="C74" s="26"/>
@@ -31740,7 +31733,7 @@
       <c r="O74" s="26"/>
       <c r="P74" s="26"/>
     </row>
-    <row r="75" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="26"/>
       <c r="B75" s="26"/>
       <c r="C75" s="60"/>
@@ -31758,7 +31751,7 @@
       <c r="O75" s="61"/>
       <c r="P75" s="26"/>
     </row>
-    <row r="76" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="26"/>
       <c r="B76" s="26"/>
       <c r="C76" s="61"/>
@@ -31776,7 +31769,7 @@
       <c r="O76" s="61"/>
       <c r="P76" s="26"/>
     </row>
-    <row r="77" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="26"/>
       <c r="B77" s="26"/>
       <c r="C77" s="61"/>
@@ -31794,7 +31787,7 @@
       <c r="O77" s="61"/>
       <c r="P77" s="26"/>
     </row>
-    <row r="78" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="26"/>
       <c r="B78" s="26"/>
       <c r="C78" s="26"/>
@@ -31812,7 +31805,7 @@
       <c r="O78" s="26"/>
       <c r="P78" s="26"/>
     </row>
-    <row r="79" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="26"/>
       <c r="B79" s="26"/>
       <c r="C79" s="64"/>
@@ -31830,7 +31823,7 @@
       <c r="O79" s="61"/>
       <c r="P79" s="26"/>
     </row>
-    <row r="80" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="26"/>
       <c r="B80" s="26"/>
       <c r="C80" s="61"/>
@@ -31848,7 +31841,7 @@
       <c r="O80" s="61"/>
       <c r="P80" s="26"/>
     </row>
-    <row r="81" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="26"/>
       <c r="B81" s="26"/>
       <c r="C81" s="26"/>
@@ -31866,7 +31859,7 @@
       <c r="O81" s="26"/>
       <c r="P81" s="26"/>
     </row>
-    <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="26"/>
       <c r="B82" s="26"/>
       <c r="C82" s="60"/>
@@ -31884,7 +31877,7 @@
       <c r="O82" s="61"/>
       <c r="P82" s="26"/>
     </row>
-    <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="26"/>
       <c r="B83" s="26"/>
       <c r="C83" s="61"/>
@@ -31902,7 +31895,7 @@
       <c r="O83" s="61"/>
       <c r="P83" s="26"/>
     </row>
-    <row r="84" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="26"/>
       <c r="B84" s="26"/>
       <c r="C84" s="61"/>
@@ -31920,7 +31913,7 @@
       <c r="O84" s="61"/>
       <c r="P84" s="26"/>
     </row>
-    <row r="85" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="26"/>
       <c r="C85" s="26"/>
       <c r="D85" s="26"/>
@@ -31937,10 +31930,10 @@
       <c r="O85" s="26"/>
       <c r="P85" s="26"/>
     </row>
-    <row r="86" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="26"/>
     </row>
-    <row r="87" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A87" s="26"/>
       <c r="B87" s="68"/>
       <c r="C87" s="61"/>
@@ -31958,7 +31951,7 @@
       <c r="O87" s="61"/>
       <c r="P87" s="61"/>
     </row>
-    <row r="88" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="26"/>
       <c r="B88" s="26"/>
       <c r="C88" s="26"/>
@@ -31976,7 +31969,7 @@
       <c r="O88" s="26"/>
       <c r="P88" s="26"/>
     </row>
-    <row r="89" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="26"/>
       <c r="B89" s="26"/>
       <c r="C89" s="26"/>
@@ -31994,7 +31987,7 @@
       <c r="O89" s="26"/>
       <c r="P89" s="26"/>
     </row>
-    <row r="90" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="26"/>
       <c r="B90" s="26"/>
       <c r="C90" s="54"/>
@@ -32012,7 +32005,7 @@
       <c r="O90" s="26"/>
       <c r="P90" s="26"/>
     </row>
-    <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26"/>
       <c r="B91" s="26"/>
       <c r="C91" s="55"/>
@@ -32030,7 +32023,7 @@
       <c r="O91" s="26"/>
       <c r="P91" s="26"/>
     </row>
-    <row r="92" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="26"/>
       <c r="B92" s="26"/>
       <c r="C92" s="26"/>
@@ -32048,7 +32041,7 @@
       <c r="O92" s="26"/>
       <c r="P92" s="26"/>
     </row>
-    <row r="93" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="26"/>
       <c r="B93" s="26"/>
       <c r="C93" s="60"/>
@@ -32066,7 +32059,7 @@
       <c r="O93" s="61"/>
       <c r="P93" s="26"/>
     </row>
-    <row r="94" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="26"/>
       <c r="B94" s="26"/>
       <c r="C94" s="61"/>
@@ -32084,7 +32077,7 @@
       <c r="O94" s="61"/>
       <c r="P94" s="26"/>
     </row>
-    <row r="95" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="26"/>
       <c r="B95" s="26"/>
       <c r="C95" s="61"/>
@@ -32102,7 +32095,7 @@
       <c r="O95" s="61"/>
       <c r="P95" s="26"/>
     </row>
-    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="26"/>
       <c r="B96" s="26"/>
       <c r="C96" s="26"/>
@@ -32120,7 +32113,7 @@
       <c r="O96" s="26"/>
       <c r="P96" s="26"/>
     </row>
-    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="26"/>
       <c r="B97" s="26"/>
       <c r="C97" s="64"/>
@@ -32138,7 +32131,7 @@
       <c r="O97" s="61"/>
       <c r="P97" s="26"/>
     </row>
-    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="26"/>
       <c r="B98" s="26"/>
       <c r="C98" s="61"/>
@@ -32156,7 +32149,7 @@
       <c r="O98" s="61"/>
       <c r="P98" s="26"/>
     </row>
-    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="26"/>
       <c r="B99" s="26"/>
       <c r="C99" s="26"/>
@@ -32174,7 +32167,7 @@
       <c r="O99" s="26"/>
       <c r="P99" s="26"/>
     </row>
-    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="26"/>
       <c r="B100" s="26"/>
       <c r="C100" s="60"/>
@@ -32192,7 +32185,7 @@
       <c r="O100" s="61"/>
       <c r="P100" s="26"/>
     </row>
-    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="26"/>
       <c r="B101" s="26"/>
       <c r="C101" s="61"/>
@@ -32210,7 +32203,7 @@
       <c r="O101" s="61"/>
       <c r="P101" s="26"/>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="26"/>
       <c r="B102" s="26"/>
       <c r="C102" s="61"/>
@@ -32228,7 +32221,7 @@
       <c r="O102" s="61"/>
       <c r="P102" s="26"/>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B103" s="26"/>
       <c r="C103" s="26"/>
       <c r="D103" s="26"/>
@@ -32245,7 +32238,7 @@
       <c r="O103" s="26"/>
       <c r="P103" s="26"/>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="26"/>
       <c r="C104" s="26"/>
       <c r="D104" s="26"/>
@@ -32262,7 +32255,7 @@
       <c r="O104" s="26"/>
       <c r="P104" s="26"/>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B105" s="68"/>
       <c r="C105" s="61"/>
       <c r="D105" s="61"/>
@@ -32279,914 +32272,914 @@
       <c r="O105" s="61"/>
       <c r="P105" s="61"/>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="99">
     <mergeCell ref="E50:F50"/>
